--- a/data/master_kanagawa.xlsx
+++ b/data/master_kanagawa.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -40,6 +40,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -60,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -72,6 +82,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -439,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -555,18 +571,32 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>シロギス 13〜23cm 20〜76匹
+アナゴ 28〜48cm 2〜26本
+LTアジ 18〜28cm 8〜89匹 ※ショート便</t>
+        </is>
+      </c>
       <c r="I2" s="3" t="inlineStr"/>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>釣りビジョン</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
       </c>
@@ -595,21 +625,44 @@
           <t>つり幸</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tsurikou.com/</t>
+        </is>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>タチウオ 70〜119cm 11〜37本 ※テンビン仕掛け
+シロギス 12〜23cm 28〜50匹</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>タチウオ船 11,000円 ※女性9,000円・中学生以下8,000円、エサ・氷付
+午前シロギス船 6,500円 ※女性5,000円、エサ・氷付
+午前/午後LTアジ船 6,500円 ※女性5,000円、エサ・氷付</t>
+        </is>
+      </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
       </c>
@@ -638,21 +691,37 @@
           <t>長八</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chohachi.co.jp/</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
+          <t>仕立中心</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>（業態メモ） ※仕立船・屋形船専門。日次の乗合釣果は非公開。シロギス・アナゴ・ハゼ等の仕立てに対応</t>
+        </is>
+      </c>
       <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
       </c>
@@ -681,21 +750,43 @@
           <t>渡辺釣船店</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>http://blog.watanabetsuribuneten.com/</t>
+        </is>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>LTアジ 18〜28cm 15〜66匹 ※午前船・横浜沖20m。午後船は31〜48匹
+カサゴ 14〜26cm 15〜44匹 ※夜カサゴ船・本牧沖10m。7月は土曜出船</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>LTアジ（午前/午後） 6,000円 ※女性5,000円・中学生以下4,000円
+LTアジ（通し） 9,000円 ※女性7,000円・中学生以下6,000円</t>
+        </is>
+      </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>釣りビジョン</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="n">
         <v>0</v>
       </c>
@@ -724,21 +815,42 @@
           <t>長崎屋</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nagasakimaru.net/</t>
+        </is>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>シロギス 14〜24cm 27〜158匹 ※トップ195匹・良型中心に好調。外道にホウボウ・アジ
+マダコ (2026-07-05) ※マダコ船出船中（7/5は2隻・予約締切）</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>シロギス船 8,500円 ※エサ・氷1個付。女性・高校生7,000円・小中学生5,000円</t>
+        </is>
+      </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
@@ -759,7 +871,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>八幡橋</t>
+          <t>新山下</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -767,21 +879,42 @@
           <t>打木屋釣船店</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.uchikiya.com/</t>
+        </is>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>シロギス 14〜23cm 18〜54匹 (2026-02-04) ※午前船
+LTアジ ※午前・午後LTアジ船が主力（数値釣果は未取得）</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>LTアジ 6,300円 ※大学・高校生5,300円・小中学生4,300円</t>
+        </is>
+      </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>釣りビジョン</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="n">
         <v>0</v>
       </c>
@@ -802,7 +935,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>八幡橋</t>
+          <t>新山下</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -810,21 +943,43 @@
           <t>広島屋</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>https://yokohama-hiroshimaya.com/</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>シロギス 13〜26cm 13〜115尾
+LTアジ 17〜33cm 10〜55尾</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>シロギス船 8,500円
+アジ船 9,000円</t>
+        </is>
+      </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>釣割</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="n">
         <v>0</v>
       </c>
@@ -855,23 +1010,35 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>http://negishimaru.com/</t>
+          <t>https://negishimaru.info/</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>LTアジ ※LTアジ・シロギス船を運航中（3〜11月は7:10出船13:30沖上がり）。数値釣果は検索から取得できず</t>
+        </is>
+      </c>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>つりー</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="n">
         <v>0</v>
       </c>
@@ -907,18 +1074,34 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>LTアジ 〜81匹 ※約4時間でトップ81匹・平均50匹前後の実績。半日船（午前/午後）</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>LTアジ半日船 6,000円 ※エサ・氷付。女性・中学生以下割引あり。JR根岸駅送迎あり</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="n">
         <v>0</v>
       </c>
@@ -955,7 +1138,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>未収集</t>
         </is>
@@ -963,7 +1146,7 @@
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -997,18 +1180,32 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>LTアジ 17〜28cm 15〜68匹 ※午前船。午後船は15〜65匹
+タチウオ 70〜95cm 11〜46本 ※ショートテンビンタチウオ船
+シロギス 14〜24cm 4〜21匹 ※午前船</t>
+        </is>
+      </c>
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>釣りビジョン</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M12" s="2" t="n">
         <v>0</v>
       </c>
@@ -1044,18 +1241,31 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>マダコ トップ7杯 (2026-06-09) ※良型でポチポチ
+タチウオ (2026-06-09) ※テンヤタチウオ好調・良型混じり</t>
+        </is>
+      </c>
       <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>釣割</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M13" s="2" t="n">
         <v>0</v>
       </c>
@@ -1091,18 +1301,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr"/>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>アジ ※年間主力はアジ・タチウオ・マダイ。船4隻で釣り物別に出船（数値釣果は未取得）</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>LTアジ 6,500円
+ルアー船 9,500円
+マダイ 11,000円</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M14" s="2" t="n">
         <v>0</v>
       </c>
@@ -1138,18 +1366,31 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>アジ 8〜32匹 ※金沢八景沖LTアジ好釣果連発
+シロギス 2〜8匹</t>
+        </is>
+      </c>
       <c r="I15" s="3" t="inlineStr"/>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
       </c>
@@ -1178,21 +1419,43 @@
           <t>野毛屋</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nogeya.com/</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>ショウサイフグ 20〜42cm 1〜13匹 ※トラフグ混じり・10匹台5名。湾フグ専門乗合で有名
+アジ 20〜28cm 15〜57匹</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>フグ船 11,000円 ※女性/高校生10,500円・中学生以下6,500円。赤エビ餌10尾付
+午前LTアジ船 6,500円 ※女性/高校生6,000円・中学生以下3,500円。餌付</t>
+        </is>
+      </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>釣りビジョン</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="n">
         <v>0</v>
       </c>
@@ -1221,21 +1484,43 @@
           <t>鴨下丸</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kamoshitamaru.com/</t>
+        </is>
+      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>タチウオ 70〜112cm 1〜21本
+アジ 18〜35cm 25〜87匹</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>ショートタチウオ船 9,500円 ※女性/高校生6,500円・大学生8,000円。餌付
+ショートLTアジ船 9,000円 ※女性/高校生6,000円・大学生7,500円。餌付</t>
+        </is>
+      </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>釣りビジョン</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M17" s="2" t="n">
         <v>0</v>
       </c>
@@ -1264,21 +1549,37 @@
           <t>弁天屋</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>https://bentenya.com/</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>アジ ※1937年創業。周年の午前午後LTアジ＋季節のタチウオ・マダイ・マゴチ・カワハギ・メバル。全日マゴチ/全日アジ/午前シロギス等で出船中（数値釣果は未取得）</t>
+        </is>
+      </c>
       <c r="I18" s="3" t="inlineStr"/>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="n">
         <v>0</v>
       </c>
@@ -1307,21 +1608,42 @@
           <t>三喜丸</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.miki-maru.net/</t>
+        </is>
+      </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>LTアジ ※LTアジ・タチウオ・マダイ中心。2026年6月はスポットイサキ五目・マダコ船も出船</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>LTアジ船 9,000円 ※女性/18歳以下6,000円
+タチウオ船 11,000円 ※女性/18歳以下9,000円</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M19" s="2" t="n">
         <v>0</v>
       </c>
@@ -1350,21 +1672,42 @@
           <t>長谷川丸</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>https://hasegawamaru.blue.coocan.jp/</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>アジ ※ショートアジ・ショートタチウオ・ショートイシモチ・日中タイラバで出船（7:20発）。ポイント近く初心者向き。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>ショートアジ/タチウオ/イシモチ船 7,500円 ※割引券可。7:20出船13:00沖上がり
+日中タイラバ船 9,000円 ※割引券可</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
       </c>
@@ -1393,21 +1736,37 @@
           <t>村上釣舟店</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chiyokichimaru.com/</t>
+        </is>
+      </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>アジ ※周年・午前/午後アジ船。ビギナー・ファミリー向き大型船。数値釣果は未取得</t>
+        </is>
+      </c>
       <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M21" s="2" t="n">
         <v>0</v>
       </c>
@@ -1436,21 +1795,37 @@
           <t>義和丸</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yokosuka.or.jp/yoshikazumaru/</t>
+        </is>
+      </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>アジ ※第三・第五義和丸の2隻。アジ・タチウオ・メバルがメイン（メバル・アジは午前午後、タチウオは午前）。数値釣果は未取得</t>
+        </is>
+      </c>
       <c r="I22" s="3" t="inlineStr"/>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M22" s="2" t="n">
         <v>0</v>
       </c>
@@ -1479,21 +1854,41 @@
           <t>こうゆう丸</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kouyuumaru.net/</t>
+        </is>
+      </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr"/>
-      <c r="I23" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>アジ 18〜49cm 25〜147匹 (2025-11-16) ※猿島周りの金アジ。ヒラメ最大1.0kg・クロダイ最大0.8kg混じり</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>ショートタチウオ船 9,000円 ※女性・子供7,000円。7:20出船</t>
+        </is>
+      </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M23" s="2" t="n">
         <v>0</v>
       </c>
@@ -1529,18 +1924,31 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>アジ 船中492〜1,026匹/日 (2026-07-04) ※7/1〜7/4の船中計。大津・猿島周りが主戦場
+タチウオ 最大123cm トップ40本 (2026-07-04) ※2番手26本・3番手23本（ルアー）。船中54〜270本/日</t>
+        </is>
+      </c>
       <c r="I24" s="3" t="inlineStr"/>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>釣割</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M24" s="2" t="n">
         <v>0</v>
       </c>
@@ -1576,18 +1984,34 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>アジ ※早朝（夏季限定）・午前・午後のアジ船ほかタチウオ・メバル等。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>（割引情報のみ） － ※女性・中学生2割引、小学生半額。料金は電話確認</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M25" s="2" t="n">
         <v>0</v>
       </c>
@@ -1616,21 +2040,37 @@
           <t>石田丸</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>http://www.ishidamaru.com/</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>アジ 20〜24cm 30〜80匹 ※18〜30cm・20〜50匹の日も。大津沖のビシアジ</t>
+        </is>
+      </c>
       <c r="I26" s="3" t="inlineStr"/>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>釣りビジョン</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M26" s="2" t="n">
         <v>0</v>
       </c>
@@ -1659,21 +2099,41 @@
           <t>まるまつ丸</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marumatsumaru.com/</t>
+        </is>
+      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr"/>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>アジ ※周年ビシアジ・初夏は夜メバル。手漕ぎ貸しボートも営業。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>午前アジ乗合船 7,000円 ※電動貸竿1,000円。土日祝7:15〜11:15、平日は3名より出船（4〜10月）</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M27" s="2" t="n">
         <v>0</v>
       </c>
@@ -1702,21 +2162,37 @@
           <t>BACH淳敏丸</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>https://bach-juntoshimaru.com/</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr"/>
+          <t>仕立中心</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>（業態メモ） ※仕立専門（アジ・マダイ等、レンタルあり）。親子2代・2隻体制。日次乗合釣果は非公開でLINE配信</t>
+        </is>
+      </c>
       <c r="I28" s="3" t="inlineStr"/>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M28" s="2" t="n">
         <v>0</v>
       </c>
@@ -1752,18 +2228,30 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>アジ 22〜33cm 50〜80匹/日 ※走水ブランドアジのビシアジ。良い日はトップ100匹前後。7:15出船・ポイントまで10分</t>
+        </is>
+      </c>
       <c r="I29" s="3" t="inlineStr"/>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M29" s="2" t="n">
         <v>0</v>
       </c>
@@ -1792,21 +2280,37 @@
           <t>政信丸</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>https://masanobumaru.net/</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>アジ 25〜30cm ※走水の黄金アジ。ほかタチウオ・マダイ（タイラバ）・シロギス・カサゴ。匹数の数値は未取得</t>
+        </is>
+      </c>
       <c r="I30" s="3" t="inlineStr"/>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M30" s="2" t="n">
         <v>0</v>
       </c>
@@ -1835,21 +2339,37 @@
           <t>第八宏二郎丸</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>https://dai8koujirou.com/</t>
+        </is>
+      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>アジ ※走水アジのほかマダイ・タチウオ・ワラサ・カワハギ。「釣らせる」と評判。数値釣果はLINE配信のみ</t>
+        </is>
+      </c>
       <c r="I31" s="3" t="inlineStr"/>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M31" s="2" t="n">
         <v>0</v>
       </c>
@@ -1878,21 +2398,37 @@
           <t>菱倉丸</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>https://hishikura-maru.com/</t>
+        </is>
+      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>アジ ※走水アジと四季の旬魚。初心者歓迎・レンタルあり。数値釣果はLINE配信のみ</t>
+        </is>
+      </c>
       <c r="I32" s="3" t="inlineStr"/>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M32" s="2" t="n">
         <v>0</v>
       </c>
@@ -1921,21 +2457,37 @@
           <t>健洋丸</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>https://kenyoumaru.com/</t>
+        </is>
+      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>タチウオ ※良型主体・大型混じり（2025年7月報告）。走水黄金アジ専門も看板。数値釣果は未取得</t>
+        </is>
+      </c>
       <c r="I33" s="3" t="inlineStr"/>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M33" s="2" t="n">
         <v>0</v>
       </c>
@@ -1964,21 +2516,41 @@
           <t>教至丸</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.noriyukimaru.net/</t>
+        </is>
+      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>アジ 22〜43cm 10〜62匹 ※走水ブランドアジ（ビシアジ）。アジ・タチウオのショートリレー便もあり</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>ショートアジ船 9,000円 ※サバ餌10尾500円別。7:15出船13:30沖上がり</t>
+        </is>
+      </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M34" s="2" t="n">
         <v>0</v>
       </c>
@@ -2007,21 +2579,41 @@
           <t>きよし丸</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kiyoshimaru.com/</t>
+        </is>
+      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr"/>
-      <c r="I35" s="3" t="inlineStr"/>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>スルメイカ ※イカ船7:20出船・15時帰港。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>イカ船 10,000円 ※女性8,000円・氷付</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M35" s="2" t="n">
         <v>0</v>
       </c>
@@ -2050,21 +2642,38 @@
           <t>黒川本家</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>https://kurokawa-maru.com/</t>
+        </is>
+      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>タチウオ 3〜31本 (2026-07-05) ※タチウオ&amp;アジリレー船。テンビン3〜31本・テンヤ3〜5本
+アジ (2026-07-05) ※小〜中アジ主体で活性良く数が伸びた（同リレー船）</t>
+        </is>
+      </c>
       <c r="I36" s="3" t="inlineStr"/>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>釣割</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M36" s="2" t="n">
         <v>0</v>
       </c>
@@ -2093,21 +2702,42 @@
           <t>平作丸</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>https://heisakumaru.jp/</t>
+        </is>
+      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr"/>
-      <c r="I37" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>マダイ 〜4.5kg トップ5匹 ※久里浜沖。トップ5匹が3人・次いで4匹と好調。ゲストにワラサ5kg</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>ワラサ（秋） 9,800円 ※コマセ・エサ付。仕立10人98,000円〜。AM7:00出船
+マダイ（秋〜春） 9,800円 ※コマセ・エサ付</t>
+        </is>
+      </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M37" s="2" t="n">
         <v>0</v>
       </c>
@@ -2128,7 +2758,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>久里浜</t>
+          <t>鴨居大室</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2136,21 +2766,37 @@
           <t>五郎丸</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gorou.co.jp/</t>
+        </is>
+      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>アジ ※ショートアジ・ショートタチウオ・イカ・日中マゴチ等で出船。数値釣果は未取得</t>
+        </is>
+      </c>
       <c r="I38" s="3" t="inlineStr"/>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr"/>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M38" s="2" t="n">
         <v>0</v>
       </c>
@@ -2179,21 +2825,37 @@
           <t>儀兵衛丸</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>https://gihee.com/</t>
+        </is>
+      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>スルメイカ ※乗合はイカ全般・ショートカワハギ。仕立はアマダイ・アジ等相談可。先着順・予約制でない。数値釣果は未取得</t>
+        </is>
+      </c>
       <c r="I39" s="3" t="inlineStr"/>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr"/>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M39" s="2" t="n">
         <v>0</v>
       </c>
@@ -2222,21 +2884,37 @@
           <t>海楽園</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>http://www.sajima-kairakuen.com/</t>
+        </is>
+      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>イサキ 15〜20匹 (2025-04-08) ※2025/3/19に15匹・4/8に20匹（カイワリ等混じり）。イナダ・カンパチ・ハナダイ・カワハギ・アカハタも。3隻体制</t>
+        </is>
+      </c>
       <c r="I40" s="3" t="inlineStr"/>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr"/>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M40" s="2" t="n">
         <v>0</v>
       </c>
@@ -2272,18 +2950,36 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>イサキ ※剣崎沖イサキ・マダイ・アジ乗合で出船中。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>イサキ乗合 10,500円
+マダイ乗合 9,500円 ※仕立80,000円
+アジ乗合 10,000円 ※仕立84,000円</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M41" s="2" t="n">
         <v>0</v>
       </c>
@@ -2319,18 +3015,35 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr"/>
-      <c r="I42" s="3" t="inlineStr"/>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>マダイ ※全長21m大型船。松輪沖のマダイ・ワラサ・マルイカ・イサキ・カワハギ等。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>マダイ乗合 10,000円 ※仕立80,000円
+イサキ乗合 11,000円</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M42" s="2" t="n">
         <v>0</v>
       </c>
@@ -2366,18 +3079,34 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr"/>
-      <c r="I43" s="3" t="inlineStr"/>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>イサキ ※梅雨時の剣崎沖イサキ好調。大型高速船3隻で周年出船。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>イサキ乗合 11,000円 ※割引で10,500円。仕立88,000円</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M43" s="2" t="n">
         <v>0</v>
       </c>
@@ -2413,18 +3142,30 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>アオリイカ 最大1.5kg トップ4杯 (2026-05-03) ※ティップラン。4/30はトップ7杯。ベニアコウ深場乗合も看板</t>
+        </is>
+      </c>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M44" s="2" t="n">
         <v>0</v>
       </c>
@@ -2460,18 +3201,34 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr"/>
-      <c r="I45" s="3" t="inlineStr"/>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr"/>
+          <t>仕立中心</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>マダイ トップ12枚 (2026-04-24) ※仕立船専門（完全予約制・ソナー装備）。メジナ・イナダ・イサキ交じり</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>仕立（人数・釣物により変動） － ※団体割引あり・要問合せ</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M45" s="2" t="n">
         <v>0</v>
       </c>
@@ -2510,15 +3267,31 @@
           <t>不明</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr"/>
-      <c r="I46" s="3" t="inlineStr"/>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>（業態メモ） ※間口港。釣果はLINE配信中心。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>仕立プラン 99,500円 ※1隻5人まで・1人増し19,900円</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M46" s="2" t="n">
         <v>0</v>
       </c>
@@ -2547,21 +3320,42 @@
           <t>瀬戸丸</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>https://sedomaru.net/</t>
+        </is>
+      </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr"/>
-      <c r="I47" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>マダイ トップ2枚 (2026-03-12) ※3隻体制（第一・第十八・第二十一）。6:30出船
+マルイカ トップ13杯 (2026-03-12) ※トップ13杯が2名</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>マダイ乗合 8,500円 ※カワハギは仕立のみ</t>
+        </is>
+      </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M47" s="2" t="n">
         <v>0</v>
       </c>
@@ -2590,21 +3384,38 @@
           <t>あまさけや丸</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amasakeyamaru.mobi/</t>
+        </is>
+      </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>イサキ 20〜35cm 23〜120匹 ※剣崎沖
+ワラサ 3.5〜5.5kg ※イサキ＆泳がせワラサリレー好調</t>
+        </is>
+      </c>
       <c r="I48" s="3" t="inlineStr"/>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>釣りビジョン</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M48" s="2" t="n">
         <v>0</v>
       </c>
@@ -2625,7 +3436,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>剣崎松輪</t>
+          <t>間口</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2633,21 +3444,37 @@
           <t>喜平治丸</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>https://kiheijimaru.co/</t>
+        </is>
+      </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>マルイカ トップ30〜40杯/日 ※全船予約乗合。アオリ・ヤリ・スミイカ・カワハギも看板</t>
+        </is>
+      </c>
       <c r="I49" s="3" t="inlineStr"/>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr"/>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>釣りビジョン</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M49" s="2" t="n">
         <v>0</v>
       </c>
@@ -2676,21 +3503,41 @@
           <t>えいあん丸</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>https://eian.jp/</t>
+        </is>
+      </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr"/>
-      <c r="I50" s="3" t="inlineStr"/>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>オニカサゴ ※通年オニカサゴ＋赤ムツ・アマダイ・アカハタ。リクエスト乗合あり。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>乗合 10,000円 ※仕立60,000円〜。各種割引あり</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M50" s="2" t="n">
         <v>0</v>
       </c>
@@ -2719,21 +3566,41 @@
           <t>愛正丸</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>https://aisho-maru.com/</t>
+        </is>
+      </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr"/>
-      <c r="I51" s="3" t="inlineStr"/>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>アマダイ ※アマダイ五目・アジ五目（クロムツ等混じり）で出船。指定席制。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>（割引情報のみ） － ※ネット割500円引・学生割・釣りガール割あり</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M51" s="2" t="n">
         <v>0</v>
       </c>
@@ -2770,7 +3637,7 @@
       </c>
       <c r="H52" s="3" t="inlineStr"/>
       <c r="I52" s="3" t="inlineStr"/>
-      <c r="J52" s="4" t="inlineStr">
+      <c r="J52" s="6" t="inlineStr">
         <is>
           <t>未収集</t>
         </is>
@@ -2813,7 +3680,7 @@
       </c>
       <c r="H53" s="3" t="inlineStr"/>
       <c r="I53" s="3" t="inlineStr"/>
-      <c r="J53" s="4" t="inlineStr">
+      <c r="J53" s="6" t="inlineStr">
         <is>
           <t>未収集</t>
         </is>
@@ -2860,7 +3727,7 @@
       </c>
       <c r="H54" s="3" t="inlineStr"/>
       <c r="I54" s="3" t="inlineStr"/>
-      <c r="J54" s="4" t="inlineStr">
+      <c r="J54" s="6" t="inlineStr">
         <is>
           <t>未収集</t>
         </is>
@@ -2907,7 +3774,7 @@
       </c>
       <c r="H55" s="3" t="inlineStr"/>
       <c r="I55" s="3" t="inlineStr"/>
-      <c r="J55" s="4" t="inlineStr">
+      <c r="J55" s="6" t="inlineStr">
         <is>
           <t>未収集</t>
         </is>
@@ -2954,7 +3821,7 @@
       </c>
       <c r="H56" s="3" t="inlineStr"/>
       <c r="I56" s="3" t="inlineStr"/>
-      <c r="J56" s="4" t="inlineStr">
+      <c r="J56" s="6" t="inlineStr">
         <is>
           <t>未収集</t>
         </is>
@@ -2997,7 +3864,7 @@
       </c>
       <c r="H57" s="3" t="inlineStr"/>
       <c r="I57" s="3" t="inlineStr"/>
-      <c r="J57" s="4" t="inlineStr">
+      <c r="J57" s="6" t="inlineStr">
         <is>
           <t>未収集</t>
         </is>
@@ -3040,7 +3907,7 @@
       </c>
       <c r="H58" s="3" t="inlineStr"/>
       <c r="I58" s="3" t="inlineStr"/>
-      <c r="J58" s="4" t="inlineStr">
+      <c r="J58" s="6" t="inlineStr">
         <is>
           <t>未収集</t>
         </is>
@@ -3083,7 +3950,7 @@
       </c>
       <c r="H59" s="3" t="inlineStr"/>
       <c r="I59" s="3" t="inlineStr"/>
-      <c r="J59" s="4" t="inlineStr">
+      <c r="J59" s="6" t="inlineStr">
         <is>
           <t>未収集</t>
         </is>
@@ -3130,7 +3997,7 @@
       </c>
       <c r="H60" s="3" t="inlineStr"/>
       <c r="I60" s="3" t="inlineStr"/>
-      <c r="J60" s="4" t="inlineStr">
+      <c r="J60" s="6" t="inlineStr">
         <is>
           <t>未収集</t>
         </is>
@@ -3173,7 +4040,7 @@
       </c>
       <c r="H61" s="3" t="inlineStr"/>
       <c r="I61" s="3" t="inlineStr"/>
-      <c r="J61" s="4" t="inlineStr">
+      <c r="J61" s="6" t="inlineStr">
         <is>
           <t>未収集</t>
         </is>
@@ -3216,7 +4083,7 @@
       </c>
       <c r="H62" s="3" t="inlineStr"/>
       <c r="I62" s="3" t="inlineStr"/>
-      <c r="J62" s="4" t="inlineStr">
+      <c r="J62" s="6" t="inlineStr">
         <is>
           <t>未収集</t>
         </is>
@@ -3259,7 +4126,7 @@
       </c>
       <c r="H63" s="3" t="inlineStr"/>
       <c r="I63" s="3" t="inlineStr"/>
-      <c r="J63" s="4" t="inlineStr">
+      <c r="J63" s="6" t="inlineStr">
         <is>
           <t>未収集</t>
         </is>
@@ -3302,7 +4169,7 @@
       </c>
       <c r="H64" s="3" t="inlineStr"/>
       <c r="I64" s="3" t="inlineStr"/>
-      <c r="J64" s="4" t="inlineStr">
+      <c r="J64" s="6" t="inlineStr">
         <is>
           <t>未収集</t>
         </is>
@@ -3345,7 +4212,7 @@
       </c>
       <c r="H65" s="3" t="inlineStr"/>
       <c r="I65" s="3" t="inlineStr"/>
-      <c r="J65" s="4" t="inlineStr">
+      <c r="J65" s="6" t="inlineStr">
         <is>
           <t>未収集</t>
         </is>
@@ -3388,7 +4255,7 @@
       </c>
       <c r="H66" s="3" t="inlineStr"/>
       <c r="I66" s="3" t="inlineStr"/>
-      <c r="J66" s="4" t="inlineStr">
+      <c r="J66" s="6" t="inlineStr">
         <is>
           <t>未収集</t>
         </is>
@@ -3435,7 +4302,7 @@
       </c>
       <c r="H67" s="3" t="inlineStr"/>
       <c r="I67" s="3" t="inlineStr"/>
-      <c r="J67" s="4" t="inlineStr">
+      <c r="J67" s="6" t="inlineStr">
         <is>
           <t>未収集</t>
         </is>
@@ -3478,7 +4345,7 @@
       </c>
       <c r="H68" s="3" t="inlineStr"/>
       <c r="I68" s="3" t="inlineStr"/>
-      <c r="J68" s="4" t="inlineStr">
+      <c r="J68" s="6" t="inlineStr">
         <is>
           <t>未収集</t>
         </is>
@@ -3521,7 +4388,7 @@
       </c>
       <c r="H69" s="3" t="inlineStr"/>
       <c r="I69" s="3" t="inlineStr"/>
-      <c r="J69" s="4" t="inlineStr">
+      <c r="J69" s="6" t="inlineStr">
         <is>
           <t>未収集</t>
         </is>
@@ -3564,7 +4431,7 @@
       </c>
       <c r="H70" s="3" t="inlineStr"/>
       <c r="I70" s="3" t="inlineStr"/>
-      <c r="J70" s="4" t="inlineStr">
+      <c r="J70" s="6" t="inlineStr">
         <is>
           <t>未収集</t>
         </is>
@@ -3607,7 +4474,7 @@
       </c>
       <c r="H71" s="3" t="inlineStr"/>
       <c r="I71" s="3" t="inlineStr"/>
-      <c r="J71" s="4" t="inlineStr">
+      <c r="J71" s="6" t="inlineStr">
         <is>
           <t>未収集</t>
         </is>
@@ -3650,7 +4517,7 @@
       </c>
       <c r="H72" s="3" t="inlineStr"/>
       <c r="I72" s="3" t="inlineStr"/>
-      <c r="J72" s="4" t="inlineStr">
+      <c r="J72" s="6" t="inlineStr">
         <is>
           <t>未収集</t>
         </is>
@@ -3693,7 +4560,7 @@
       </c>
       <c r="H73" s="3" t="inlineStr"/>
       <c r="I73" s="3" t="inlineStr"/>
-      <c r="J73" s="4" t="inlineStr">
+      <c r="J73" s="6" t="inlineStr">
         <is>
           <t>未収集</t>
         </is>
@@ -3736,7 +4603,7 @@
       </c>
       <c r="H74" s="3" t="inlineStr"/>
       <c r="I74" s="3" t="inlineStr"/>
-      <c r="J74" s="4" t="inlineStr">
+      <c r="J74" s="6" t="inlineStr">
         <is>
           <t>未収集</t>
         </is>
@@ -3779,7 +4646,7 @@
       </c>
       <c r="H75" s="3" t="inlineStr"/>
       <c r="I75" s="3" t="inlineStr"/>
-      <c r="J75" s="4" t="inlineStr">
+      <c r="J75" s="6" t="inlineStr">
         <is>
           <t>未収集</t>
         </is>
@@ -3822,7 +4689,7 @@
       </c>
       <c r="H76" s="3" t="inlineStr"/>
       <c r="I76" s="3" t="inlineStr"/>
-      <c r="J76" s="4" t="inlineStr">
+      <c r="J76" s="6" t="inlineStr">
         <is>
           <t>未収集</t>
         </is>
@@ -3830,6 +4697,1298 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>横浜市</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>八幡橋</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>濱生丸</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr"/>
+      <c r="I77" s="3" t="inlineStr"/>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>横浜市</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>八幡橋</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>鴨下丸kawana</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr"/>
+      <c r="I78" s="3" t="inlineStr"/>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>横浜市</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>根岸</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>第三鴨下丸</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>https://3kamoshitamaru.jimdofree.com/</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr"/>
+      <c r="I79" s="3" t="inlineStr"/>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>横浜市</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>金沢漁港</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>仁丸</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>https://dai1hitoshi.com/</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr"/>
+      <c r="I80" s="3" t="inlineStr"/>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>横浜市</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>金沢八景</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>荒川屋</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arakawaya.jp/</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr"/>
+      <c r="I81" s="3" t="inlineStr"/>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>横浜市</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>新山下</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>横浜黒川本家</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>https://kurokawahonke.com/</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr"/>
+      <c r="I82" s="3" t="inlineStr"/>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>横浜市</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>小柴</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>小柴丸</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>http://koshibamaru.yokohama/</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr"/>
+      <c r="I83" s="3" t="inlineStr"/>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>横須賀市</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>横須賀</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>すえじ丸</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>https://suejimaru.com/</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr"/>
+      <c r="I84" s="3" t="inlineStr"/>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>横浜市</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>金沢漁港</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>横内丸</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr"/>
+      <c r="I85" s="3" t="inlineStr"/>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>横須賀市</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>走水</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>治丸</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr"/>
+      <c r="I86" s="3" t="inlineStr"/>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>横須賀市</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>走水</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>高司丸</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.takajimaru.net/</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr"/>
+      <c r="I87" s="3" t="inlineStr"/>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>横須賀市</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>鴨居大室</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>一郎丸（鴨居）</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ichiroumaru.jp/</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr"/>
+      <c r="I88" s="3" t="inlineStr"/>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>横須賀市</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>鴨居大室</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>房丸</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>https://kamoi-fusamaru.com/</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr"/>
+      <c r="I89" s="3" t="inlineStr"/>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>横須賀市</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>鴨居</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>かもい丸</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kamoimaru.com/</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr"/>
+      <c r="I90" s="3" t="inlineStr"/>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>横須賀市</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>久里浜</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>網屋丸</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>https://amiyamaru.com/</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr"/>
+      <c r="I91" s="3" t="inlineStr"/>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>横須賀市</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>久里浜</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>ムツ六釣船店</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>http://www.mutsuroku.com/</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr"/>
+      <c r="I92" s="3" t="inlineStr"/>
+      <c r="J92" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>横須賀市</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>長井漆山</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>かねい丸</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>https://kaneimaru.com/</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr"/>
+      <c r="I93" s="3" t="inlineStr"/>
+      <c r="J93" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>横須賀市</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>長井</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>はら丸</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.haramaru.net/</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr"/>
+      <c r="I94" s="3" t="inlineStr"/>
+      <c r="J94" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>横須賀市</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>長井漆山</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>春盛丸</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>https://haruseimaru.com/</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr"/>
+      <c r="I95" s="3" t="inlineStr"/>
+      <c r="J95" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>横須賀市</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>長井漆山</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>光三丸</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mitsuzou.jp/</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr"/>
+      <c r="I96" s="3" t="inlineStr"/>
+      <c r="J96" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>横須賀市</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>佐島</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>深田家</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fukadaya.mobi/</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr"/>
+      <c r="I97" s="3" t="inlineStr"/>
+      <c r="J97" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>三浦市</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>松輪江奈</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>新徳丸</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>https://shintokumaru.jp/</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr"/>
+      <c r="I98" s="3" t="inlineStr"/>
+      <c r="J98" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>三浦市</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>松輪江奈</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>一義丸</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>https://kazuyoshimaru.com/</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr"/>
+      <c r="I99" s="3" t="inlineStr"/>
+      <c r="J99" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>三浦市</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>松輪</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>浜鈴丸</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr"/>
+      <c r="I100" s="3" t="inlineStr"/>
+      <c r="J100" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>三浦市</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>剣崎松輪</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>太郎八丸</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tarohachimaru.com/</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr"/>
+      <c r="I101" s="3" t="inlineStr"/>
+      <c r="J101" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>三浦市</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>剣崎松輪</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>鈴米丸</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.suzuyonemaru.com/</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr"/>
+      <c r="I102" s="3" t="inlineStr"/>
+      <c r="J102" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>三浦市</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>三崎諸磯</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>光ニ丸</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mitsuzimaru.com/</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr"/>
+      <c r="I103" s="3" t="inlineStr"/>
+      <c r="J103" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>三浦市</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>間口</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>強丸</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr"/>
+      <c r="I104" s="3" t="inlineStr"/>
+      <c r="J104" s="6" t="inlineStr">
+        <is>
+          <t>未収集</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/master_kanagawa.xlsx
+++ b/data/master_kanagawa.xlsx
@@ -54,7 +54,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M104"/>
+  <dimension ref="A1:M124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1136,17 +1136,29 @@
           <t>不明</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>（メモ） ※Web検索3回で該当船宿を確認できず（廃業または初期リスト誤記の可能性）</t>
+        </is>
+      </c>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+          <t>取得不可</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -3629,21 +3641,37 @@
           <t>たいぞう丸</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>https://taizoumaru.com/</t>
+        </is>
+      </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>アマダイ ※年間通しアマダイ・マルイカ・キハダ/本ガツオ。冬場は大型アマダイ狙いで定評。数値釣果は未取得</t>
+        </is>
+      </c>
       <c r="I52" s="3" t="inlineStr"/>
-      <c r="J52" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr"/>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M52" s="2" t="n">
         <v>0</v>
       </c>
@@ -3672,21 +3700,43 @@
           <t>太郎丸</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>https://kotsubo-taromaru.com/</t>
+        </is>
+      </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr"/>
-      <c r="I53" s="3" t="inlineStr"/>
-      <c r="J53" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>キンメダイ 28〜40cm 6〜17匹 (2026-02-14)
+クロムツ 34〜45cm 0〜8匹 (2026-02-14)</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>キンメ・ムツ五目船 14,000円 ※エサ・氷付。3名以上で出船確定・現金のみ
+沖の瀬ウィリー五目船 13,000円 ※エサ・氷付</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M53" s="2" t="n">
         <v>0</v>
       </c>
@@ -3722,18 +3772,35 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr"/>
-      <c r="I54" s="3" t="inlineStr"/>
-      <c r="J54" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>アマダイ 22〜38cm ※カイワリ＆アマダイ五目に通年出船。アジ・サバ・イサキ混じり
+カイワリ ※同五目船の主対象</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>カイワリ＆アマダイ五目 11,500円 ※餌・氷・仕掛け付。女性・中学生以下2,000円引</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M54" s="2" t="n">
         <v>0</v>
       </c>
@@ -3769,18 +3836,34 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr"/>
-      <c r="I55" s="3" t="inlineStr"/>
-      <c r="J55" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>アジ 35〜38cm 約30匹 ※アジ＆マダイ五目（ビシアジ）。ワラサ・イシナギ混じり</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>アジ＆マダイ五目 11,000円 ※7:00出船14:00納竿。女性・中学生以下2,000円引。貸道具1,000円</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M55" s="2" t="n">
         <v>0</v>
       </c>
@@ -3816,18 +3899,36 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr"/>
-      <c r="I56" s="3" t="inlineStr"/>
-      <c r="J56" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>アジ 25〜40cm 0〜13匹 (2026-07-01)
+アマダイ 27〜40cm 0〜2匹 (2026-07-01)
+ハナダイ 28〜32cm 0〜2匹 (2026-07-01)</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>貸切（11人まで） 85,000円 ※1隻料金。12〜19人96,000円。乗合はヒラメ泳がせ等</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>釣割</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M56" s="2" t="n">
         <v>0</v>
       </c>
@@ -3856,21 +3957,41 @@
           <t>孝太郎丸</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>https://koutaroumaru.net/</t>
+        </is>
+      </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr"/>
-      <c r="I57" s="3" t="inlineStr"/>
-      <c r="J57" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>マダイ ※オキアミ喰わせマダイで有名。季節でアマダイ・シロギス・カサゴ等。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>タイ船 11,000円</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M57" s="2" t="n">
         <v>0</v>
       </c>
@@ -3899,21 +4020,37 @@
           <t>島きち丸</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>https://shimakichimaru.com/</t>
+        </is>
+      </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>アジ ※4隻体制。アジ・キス・ライトルアー・ムギイカ/スルメ、8月〜キハダ・カツオ、9月〜カワハギ・アマダイ。数値釣果は未取得</t>
+        </is>
+      </c>
       <c r="I58" s="3" t="inlineStr"/>
-      <c r="J58" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr"/>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M58" s="2" t="n">
         <v>0</v>
       </c>
@@ -3945,18 +4082,30 @@
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>アジ ※アジ・カワハギ・アマダイ・イナダ・カツオ等。ショートキス便あり。数値釣果は未取得</t>
+        </is>
+      </c>
       <c r="I59" s="3" t="inlineStr"/>
-      <c r="J59" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="2" t="inlineStr"/>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>釣りビジョン</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M59" s="2" t="n">
         <v>0</v>
       </c>
@@ -3992,18 +4141,30 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>キハダ ※キハダ・ライト五目等で出船中（釣果速報はブログ/Instagram配信）。数値釣果は未取得</t>
+        </is>
+      </c>
       <c r="I60" s="3" t="inlineStr"/>
-      <c r="J60" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="inlineStr"/>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M60" s="2" t="n">
         <v>0</v>
       </c>
@@ -4032,21 +4193,41 @@
           <t>ちがさき丸</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>https://chigasakimaru.com/</t>
+        </is>
+      </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr"/>
-      <c r="I61" s="3" t="inlineStr"/>
-      <c r="J61" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>アジ トップ73匹 ※終日アタリ良くポツポツ</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>乗合 10,000円 ※〜。貸切110,000円〜</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M61" s="2" t="n">
         <v>0</v>
       </c>
@@ -4075,21 +4256,41 @@
           <t>まごうの丸</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.magounomaru.net/</t>
+        </is>
+      </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr"/>
-      <c r="I62" s="3" t="inlineStr"/>
-      <c r="J62" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>アジ 20〜38cm 15〜42匹 ※ビシアジ船。貸竿客も好釣果</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>シロギス船 8,500円 ※エサ別・氷1個付。女性・高校生・子供6,000円</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M62" s="2" t="n">
         <v>0</v>
       </c>
@@ -4118,21 +4319,37 @@
           <t>沖右ヱ門丸</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.okiemonmaru.com/</t>
+        </is>
+      </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>キハダ ※キハダ（カツオ混じり）・アオリイカ・ビシアジ・タイ・ワラサ。LT船はイナダ・ショゴも。数値釣果は未取得</t>
+        </is>
+      </c>
       <c r="I63" s="3" t="inlineStr"/>
-      <c r="J63" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="2" t="inlineStr"/>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M63" s="2" t="n">
         <v>0</v>
       </c>
@@ -4161,21 +4378,42 @@
           <t>庄三郎丸</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.shouzaburo.com/</t>
+        </is>
+      </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr"/>
-      <c r="I64" s="3" t="inlineStr"/>
-      <c r="J64" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>アジ 26〜40cm 14〜32匹 ※ハナダイ・マダイ・イトヨリ・大サバ混じり</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>ライト五目船 12,000円 ※6:30出船・アミコマセ付
+ヒラメ・カサゴ五目船 11,000円 ※6:30出船</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M64" s="2" t="n">
         <v>0</v>
       </c>
@@ -4204,21 +4442,41 @@
           <t>庄治郎丸</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>https://shojiromaru.net/</t>
+        </is>
+      </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr"/>
-      <c r="I65" s="3" t="inlineStr"/>
-      <c r="J65" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr"/>
-      <c r="L65" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>アジ 28〜40cm 15〜58匹 ※良型主体で絶好調。マダイ1.2〜1.5kg 0〜1枚・ハナダイ0〜2枚混じり</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>乗合（成人男性・予約） 10,500円 ※予約なし11,000円。大学生・女性・高校生8,000円。平日ペア割2名15,000円</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M65" s="2" t="n">
         <v>0</v>
       </c>
@@ -4247,21 +4505,41 @@
           <t>豊漁丸</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>http://www.houryomaru.co.jp/</t>
+        </is>
+      </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr"/>
-      <c r="I66" s="3" t="inlineStr"/>
-      <c r="J66" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>アジ ※アジ・クロダイ・ハナダイ・ヒラメ・サバ・シロギス・ホウボウ等。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>乗合（釣割価格） 7,500円 ※〜</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>釣割</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M66" s="2" t="n">
         <v>0</v>
       </c>
@@ -4297,18 +4575,34 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr"/>
-      <c r="I67" s="3" t="inlineStr"/>
-      <c r="J67" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr"/>
-      <c r="L67" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>（五目） ※誰もが楽しめる五目釣り中心。釣果はLINE配信。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>乗合（釣割価格） 4,500円 ※〜</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M67" s="2" t="n">
         <v>0</v>
       </c>
@@ -4337,21 +4631,37 @@
           <t>浅八丸</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>https://asa8.net/</t>
+        </is>
+      </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>イサキ ※イサキ等の対象魚で出船中。数値釣果は未取得</t>
+        </is>
+      </c>
       <c r="I68" s="3" t="inlineStr"/>
-      <c r="J68" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="2" t="inlineStr"/>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M68" s="2" t="n">
         <v>0</v>
       </c>
@@ -4380,21 +4690,41 @@
           <t>五平丸</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>https://goheimaru.com/</t>
+        </is>
+      </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr"/>
-      <c r="I69" s="3" t="inlineStr"/>
-      <c r="J69" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr"/>
-      <c r="L69" s="2" t="inlineStr"/>
+          <t>仕立中心</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>（業態メモ） ※貸切専門船。日次の乗合釣果は非公開</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>貸切（1人あたり） 8,000円 ※〜。釣割価格10,000円/人〜</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M69" s="2" t="n">
         <v>0</v>
       </c>
@@ -4423,21 +4753,42 @@
           <t>邦丸</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>https://kunimaru-oiso.amebaownd.com/</t>
+        </is>
+      </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr"/>
-      <c r="I70" s="3" t="inlineStr"/>
-      <c r="J70" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>（ルアー五目） ※ショートルアー・ショート根魚乗合で出船。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>ショートルアー乗合 7,500円 ※女性/高校生7,000円・中学生以下6,000円。6:00〜11:00
+ショート根魚乗合 8,000円 ※付けエサ付。ルアー/女性/高校生7,500円</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M70" s="2" t="n">
         <v>0</v>
       </c>
@@ -4466,21 +4817,41 @@
           <t>とうふや丸</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.scn-net.ne.jp/~tofuya/</t>
+        </is>
+      </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr"/>
-      <c r="I71" s="3" t="inlineStr"/>
-      <c r="J71" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>アジ ※アジ・カンコ・ワラサ・オニカサゴ等。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>アジ船 9,000円 ※エサ付。女性・子供3,000円引。3名グループ500円引/5名1,000円引</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M71" s="2" t="n">
         <v>0</v>
       </c>
@@ -4509,21 +4880,41 @@
           <t>平安丸</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>https://heian-maru.com/</t>
+        </is>
+      </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr"/>
-      <c r="I72" s="3" t="inlineStr"/>
-      <c r="J72" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>スルメイカ ※スルメ・キンメ・クロムツ・メダイ中心。アマダイ・ビシアジ・LT五目も。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>感謝デー スルメイカ/ビシアジ船 8,000円 ※通常料金は要確認</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M72" s="2" t="n">
         <v>0</v>
       </c>
@@ -4552,21 +4943,37 @@
           <t>藤八丸</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>https://touhachimaru.com/</t>
+        </is>
+      </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr"/>
+          <t>仕立中心</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>（業態メモ） ※船一隻貸切利用が基本。夏キハダ・冬アマダイ等。レンタルあり</t>
+        </is>
+      </c>
       <c r="I73" s="3" t="inlineStr"/>
-      <c r="J73" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="2" t="inlineStr"/>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M73" s="2" t="n">
         <v>0</v>
       </c>
@@ -4595,21 +5002,37 @@
           <t>坂口丸</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>https://sakaguchimaru.com/</t>
+        </is>
+      </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>ムギイカ ※ムギイカ・ヤリイカ等の実績。キハダ・アマダイ・イナダ・アジ・オニカサゴも。全船予約制。数値釣果は未取得</t>
+        </is>
+      </c>
       <c r="I74" s="3" t="inlineStr"/>
-      <c r="J74" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="inlineStr"/>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M74" s="2" t="n">
         <v>0</v>
       </c>
@@ -4638,21 +5061,37 @@
           <t>八隆丸</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>https://hachitakamaru.com/</t>
+        </is>
+      </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>ムギイカ ※11トン船。乗合・貸切両対応。マダイ・アジサバ・シロギス五目も。数値釣果は未取得</t>
+        </is>
+      </c>
       <c r="I75" s="3" t="inlineStr"/>
-      <c r="J75" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr"/>
-      <c r="L75" s="2" t="inlineStr"/>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M75" s="2" t="n">
         <v>0</v>
       </c>
@@ -4681,21 +5120,41 @@
           <t>緑龍丸</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>https://ryokuryumaru.jp/</t>
+        </is>
+      </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr"/>
-      <c r="I76" s="3" t="inlineStr"/>
-      <c r="J76" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>ベニアコウ ※1993年開業・深場釣りで定評（ベニアコウ・大型ムツ等）。真鶴岩港。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>乗合 10,000円 ※仕立50,000円（5人まで・1人増し10,000円、春秋）</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M76" s="2" t="n">
         <v>0</v>
       </c>
@@ -4724,21 +5183,37 @@
           <t>濱生丸</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hamaseimaru.com/</t>
+        </is>
+      </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>マゴチ ※13トン船。マゴチ主力＋夜アナゴ・マダコ・シロギス&amp;マゴチリレー等。数値釣果は未取得</t>
+        </is>
+      </c>
       <c r="I77" s="3" t="inlineStr"/>
-      <c r="J77" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr"/>
-      <c r="L77" s="2" t="inlineStr"/>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M77" s="2" t="n">
         <v>0</v>
       </c>
@@ -4767,21 +5242,41 @@
           <t>鴨下丸kawana</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>https://kawana913.amebaownd.com/</t>
+        </is>
+      </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr"/>
-      <c r="I78" s="3" t="inlineStr"/>
-      <c r="J78" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>マダコ 0.3〜3.2kg 1〜8杯 (2026-06-30) ※2026年6月の実績レンジ。マダイ・タチウオも専門</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>マダイ 11,500円 ※レンタル竿・キーパー・ビシ一式1,500円</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>釣割</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M78" s="2" t="n">
         <v>0</v>
       </c>
@@ -4817,18 +5312,35 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr"/>
-      <c r="I79" s="3" t="inlineStr"/>
-      <c r="J79" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>青物五目 1〜10匹 ※2026年5月下旬〜6月初旬の実績。ルアー専門船（ジギング/キャスティング）。イナダ・ワラサ・ブリ・サワラ・カンパチ</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>ルアー青物船 10,000円 ※7:00出船16:00前後帰港
+タチウオ船 10,000円 ※中学生以下8,000円。14:30前後帰港</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M79" s="2" t="n">
         <v>0</v>
       </c>
@@ -4864,18 +5376,34 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr"/>
-      <c r="I80" s="3" t="inlineStr"/>
-      <c r="J80" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>アジ ※LTアジ専門（船長歴30年）。クロダイも。釣果はLINE配信。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>LTアジ乗合 8,500円 ※仕立もあり。木曜定休</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M80" s="2" t="n">
         <v>0</v>
       </c>
@@ -4906,23 +5434,39 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>https://www.arakawaya.jp/</t>
+          <t>https://arakawaya.jp/</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr"/>
-      <c r="I81" s="3" t="inlineStr"/>
-      <c r="J81" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>アジ 19〜40cm 5〜50匹 (2026-06-21) ※1958年創業。釣った魚をさばいて食べられる。午前/午後アジ・シロギス船</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>ショートアジ 9,500円 ※エサ・氷付</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M81" s="2" t="n">
         <v>0</v>
       </c>
@@ -4958,18 +5502,30 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>（五目） ※江戸末期創業・3隻体制。季節の出船情報は公式料金表ページに掲載。数値釣果は未取得</t>
+        </is>
+      </c>
       <c r="I82" s="3" t="inlineStr"/>
-      <c r="J82" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="2" t="inlineStr"/>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M82" s="2" t="n">
         <v>0</v>
       </c>
@@ -5005,18 +5561,31 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>イシモチ 19〜35cm 2〜11匹 ※2026年6月〜マダコ・アジ・イシモチ・シロギス船で出船
+マダコ ※6月からマダコ船出船</t>
+        </is>
+      </c>
       <c r="I83" s="3" t="inlineStr"/>
-      <c r="J83" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr"/>
-      <c r="L83" s="2" t="inlineStr"/>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>釣りビジョン</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M83" s="2" t="n">
         <v>0</v>
       </c>
@@ -5037,7 +5606,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>横須賀</t>
+          <t>長井漆山</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -5052,18 +5621,34 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr"/>
-      <c r="I84" s="3" t="inlineStr"/>
-      <c r="J84" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr"/>
-      <c r="L84" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>ヤリイカ 21〜41cm 1〜11杯 ※城ヶ島西沖〜長井西沖110〜160m。季節でムギ・スルメ・ヤリ</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>イカ乗合 10,000円 ※氷付。女性6,500円・ブログのキーワード割9,000円。電動貸竿2,000円</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M84" s="2" t="n">
         <v>0</v>
       </c>
@@ -5095,18 +5680,34 @@
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr"/>
-      <c r="I85" s="3" t="inlineStr"/>
-      <c r="J85" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr"/>
-      <c r="L85" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>マダコ トップ117匹 ※10匹以上9人・良型多数、船中194匹（両舷計）。2010年開業のマダコ乗合が看板</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>（レンタル料のみ判明） － ※貸竿500円・エギ3個1,000円・エギセット1,500円。乗合料金は要確認</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>釣りビジョン</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M85" s="2" t="n">
         <v>0</v>
       </c>
@@ -5135,21 +5736,41 @@
           <t>治丸</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>https://osamumaru.jp/</t>
+        </is>
+      </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr"/>
-      <c r="I86" s="3" t="inlineStr"/>
-      <c r="J86" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="2" t="inlineStr"/>
+          <t>仕立中心</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>（業態メモ） ※貸切専門。週末中心にアジ等へ出船</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>貸切（平日・1人あたり） 6,000円 ※〜</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M86" s="2" t="n">
         <v>0</v>
       </c>
@@ -5185,18 +5806,30 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H87" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>アジ 23〜30cm 15〜25匹 ※走水〜観音崎沖のブランドアジを周年。ショート便</t>
+        </is>
+      </c>
       <c r="I87" s="3" t="inlineStr"/>
-      <c r="J87" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr"/>
-      <c r="L87" s="2" t="inlineStr"/>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>釣りビジョン</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M87" s="2" t="n">
         <v>0</v>
       </c>
@@ -5232,18 +5865,30 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>トラフグ ※創業80年超の老舗。トラフグ・フグ乗合が看板（3名から出船）。数値釣果は未取得</t>
+        </is>
+      </c>
       <c r="I88" s="3" t="inlineStr"/>
-      <c r="J88" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="inlineStr"/>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M88" s="2" t="n">
         <v>0</v>
       </c>
@@ -5279,18 +5924,30 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H89" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>（五目） ※鴨居大室港。釣果はLINE配信。レンタル充実（手巻800円/電動1,800円）。数値釣果は未取得</t>
+        </is>
+      </c>
       <c r="I89" s="3" t="inlineStr"/>
-      <c r="J89" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="2" t="inlineStr"/>
+      <c r="J89" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M89" s="2" t="n">
         <v>0</v>
       </c>
@@ -5326,18 +5983,30 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>（五目） ※鴨居港の乗合船。数値釣果は未取得</t>
+        </is>
+      </c>
       <c r="I90" s="3" t="inlineStr"/>
-      <c r="J90" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="2" t="inlineStr"/>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>釣りビジョン</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M90" s="2" t="n">
         <v>0</v>
       </c>
@@ -5373,18 +6042,34 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H91" s="3" t="inlineStr"/>
-      <c r="I91" s="3" t="inlineStr"/>
-      <c r="J91" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>マダイ ※コマセマダイ乗合（外道にアマダイ）。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>マダイ乗合 9,800円</t>
+        </is>
+      </c>
+      <c r="J91" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M91" s="2" t="n">
         <v>0</v>
       </c>
@@ -5420,18 +6105,34 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr"/>
-      <c r="I92" s="3" t="inlineStr"/>
-      <c r="J92" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>アマダイ ※アマダイ等で出船。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>アマダイ仕立 8,700円 ※1人あたり</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M92" s="2" t="n">
         <v>0</v>
       </c>
@@ -5467,18 +6168,34 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H93" s="3" t="inlineStr"/>
-      <c r="I93" s="3" t="inlineStr"/>
-      <c r="J93" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K93" s="2" t="inlineStr"/>
-      <c r="L93" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>マグロ ※3隻体制。ルアー/コマセマグロ対応。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>仕立（11〜6月・終日5人まで） 50,000円 ※1人増10,000円。7〜10月は6人60,000円。氷・おみやげ付</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M93" s="2" t="n">
         <v>0</v>
       </c>
@@ -5514,18 +6231,34 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H94" s="3" t="inlineStr"/>
-      <c r="I94" s="3" t="inlineStr"/>
-      <c r="J94" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K94" s="2" t="inlineStr"/>
-      <c r="L94" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>マルイカ ※ムギ・スルメ・マル・ヤリイカ中心のイカ船（6時出船）。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>イカ船 9,500円 ※氷付</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M94" s="2" t="n">
         <v>0</v>
       </c>
@@ -5561,18 +6294,30 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H95" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>ヤリイカ ※沖のイカ（ヤリ・スルメ）専門船。マルイカ・アオリ・カワハギ・根魚も。数値釣果は未取得</t>
+        </is>
+      </c>
       <c r="I95" s="3" t="inlineStr"/>
-      <c r="J95" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K95" s="2" t="inlineStr"/>
-      <c r="L95" s="2" t="inlineStr"/>
+      <c r="J95" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M95" s="2" t="n">
         <v>0</v>
       </c>
@@ -5603,23 +6348,35 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>https://www.mitsuzou.jp/</t>
+          <t>https://mitsuzou.com/</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H96" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>スルメイカ ※イカ釣りメイン。数値釣果は未取得</t>
+        </is>
+      </c>
       <c r="I96" s="3" t="inlineStr"/>
-      <c r="J96" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K96" s="2" t="inlineStr"/>
-      <c r="L96" s="2" t="inlineStr"/>
+      <c r="J96" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M96" s="2" t="n">
         <v>0</v>
       </c>
@@ -5655,18 +6412,36 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H97" s="3" t="inlineStr"/>
-      <c r="I97" s="3" t="inlineStr"/>
-      <c r="J97" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr"/>
-      <c r="L97" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>ヒラメ ※ヒラメ・イサキ・メジナ・アジ・シロギス等。前日20時まで予約制。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>ヒラメ船 13,000円 ※6時出船・餌氷付
+カワハギ船 9,000円 ※氷付
+LT五目船 10,000円 ※餌氷付</t>
+        </is>
+      </c>
+      <c r="J97" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M97" s="2" t="n">
         <v>0</v>
       </c>
@@ -5702,18 +6477,34 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="inlineStr"/>
-      <c r="I98" s="3" t="inlineStr"/>
-      <c r="J98" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="2" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>イサキ 23〜36cm 38〜100匹 (2026-07-04) ※7/3は23〜38cm・25〜100匹。ビギナー歓迎</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>ワラサ・マダイ乗合 10,000円</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M98" s="2" t="n">
         <v>0</v>
       </c>
@@ -5749,18 +6540,30 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H99" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>イサキ ※キハダ・マダイ・ライトイサキ・マルイカ等。数値釣果は未取得</t>
+        </is>
+      </c>
       <c r="I99" s="3" t="inlineStr"/>
-      <c r="J99" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr"/>
-      <c r="L99" s="2" t="inlineStr"/>
+      <c r="J99" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>釣りビジョン</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M99" s="2" t="n">
         <v>0</v>
       </c>
@@ -5792,18 +6595,30 @@
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H100" s="3" t="inlineStr"/>
+          <t>仕立中心</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>（業態メモ） ※貸切専門。剣崎沖のマダイ・ワラサ・イサキ等</t>
+        </is>
+      </c>
       <c r="I100" s="3" t="inlineStr"/>
-      <c r="J100" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="2" t="inlineStr"/>
+      <c r="J100" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M100" s="2" t="n">
         <v>0</v>
       </c>
@@ -5839,18 +6654,30 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H101" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>アオリイカ ※ティップラン等で出船。数値釣果は未取得</t>
+        </is>
+      </c>
       <c r="I101" s="3" t="inlineStr"/>
-      <c r="J101" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K101" s="2" t="inlineStr"/>
-      <c r="L101" s="2" t="inlineStr"/>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M101" s="2" t="n">
         <v>0</v>
       </c>
@@ -5886,18 +6713,30 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H102" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>イシダイ ※2026/5/24に石鯛狙い等の実績。数値釣果は未取得</t>
+        </is>
+      </c>
       <c r="I102" s="3" t="inlineStr"/>
-      <c r="J102" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K102" s="2" t="inlineStr"/>
-      <c r="L102" s="2" t="inlineStr"/>
+      <c r="J102" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M102" s="2" t="n">
         <v>0</v>
       </c>
@@ -5933,18 +6772,30 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H103" s="3" t="inlineStr"/>
+          <t>仕立中心</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>（業態メモ） ※仕立船専門（三崎諸磯）。日次乗合釣果は非公開</t>
+        </is>
+      </c>
       <c r="I103" s="3" t="inlineStr"/>
-      <c r="J103" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr"/>
-      <c r="L103" s="2" t="inlineStr"/>
+      <c r="J103" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M103" s="2" t="n">
         <v>0</v>
       </c>
@@ -5976,19 +6827,1234 @@
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H104" s="3" t="inlineStr"/>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>マダイ ※型見ずなしの好調。クロダイ・メジナ・イサキ混じり。タチウオ・サワラも。要2日前予約</t>
+        </is>
+      </c>
       <c r="I104" s="3" t="inlineStr"/>
-      <c r="J104" s="6" t="inlineStr">
-        <is>
-          <t>未収集</t>
-        </is>
-      </c>
-      <c r="K104" s="2" t="inlineStr"/>
-      <c r="L104" s="2" t="inlineStr"/>
+      <c r="J104" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>釣りビジョン</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="M104" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>葉山町</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>葉山鐙摺</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>秀吉丸</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hidekichimaru.com/</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>マダイ ※マダイ・イサキ・アマダイ・イカ・ヒラメ等の実績記録あり。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr"/>
+      <c r="J105" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>葉山町</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>葉山鐙摺</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>長三朗丸</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chozaburomaru.com/</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>ヤリイカ ※ヤリ・スルメ・マルイカ、アマダイ、キハダ・カツオ等。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I106" s="3" t="inlineStr"/>
+      <c r="J106" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>鎌倉市</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>腰越</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>政美丸</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.masamimaru.com/</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>（LTウィリー五目） ※2隻体制（10名/14名限定）・中乗り付きで初心者向き。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>LTウィリー五目船 11,000円 ※女性・高校生9,000円・小中学生8,000円。餌氷付。5:45〜6:15出船</t>
+        </is>
+      </c>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>藤沢市</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>片瀬江ノ島</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>ゆうせい丸</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>https://yuusei-maru.net/</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>マダイ ※マダイ・マダコ・アナゴ・ヒラメ&amp;根魚等の各種乗合。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>マダイ船 11,500円 ※6:00出船。女性9,500円・中学生8,500円
+マダコ船 11,000円 ※6:30出船
+アナゴ船 10,500円 ※6:30出船</t>
+        </is>
+      </c>
+      <c r="J108" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>小田原市</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>早川</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>おおもり丸</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>https://www2.hp-ez.com/hp/oomorimaru/</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>アマダイ 27〜37cm 2〜6匹 ※ゲストにイトヨリ・マゴチ・ヒメコダイ
+イトヨリ 22〜38cm 7〜14匹</t>
+        </is>
+      </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>乗合 11,000円 ※氷1個付・付餌別500〜700円。6:30出船</t>
+        </is>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>小田原市</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>小田原</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>海真丸</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kaishinmaru.com/</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>仕立中心</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>（業態メモ） ※貸切船（大人5名から仕立・定員12名）。アジ・サバ・シロギス・ワカシ・イナダ等</t>
+        </is>
+      </c>
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t>仕立（1人あたり） 10,000円 ※税込。竿・仕掛けの用意あり</t>
+        </is>
+      </c>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>真鶴町</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>真鶴</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>第八緑龍丸</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>https://ryokuryu2.com/</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>（五目） ※貸切・乗合両対応。キャビン・ソナー等設備充実。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="inlineStr"/>
+      <c r="J111" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>真鶴町</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>真鶴</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>国敏丸</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kunitoshimaru.mobi/</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>マダイ ※ライト深場五目・マダイ・イカ等で出船。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I112" s="3" t="inlineStr"/>
+      <c r="J112" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>真鶴町</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>真鶴</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>誠いち丸</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>https://seiichimaru.com/</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>（五目） ※真鶴港の乗合船。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="inlineStr"/>
+      <c r="J113" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>横浜市</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>金沢漁港</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>進丸</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>https://susumumaru.com/</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>シロギス ※初心者・女性・家族歓迎（レンタル込み手ぶらOK）。シロギス・アジ・イシモチ等。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I114" s="3" t="inlineStr"/>
+      <c r="J114" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>横浜市</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>金沢八景</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>新健丸</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>http://emowest.xsrv.jp/</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>（五目） ※金沢八景・駅徒歩3分。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I115" s="3" t="inlineStr"/>
+      <c r="J115" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>横浜市</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>金沢八景</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>黒川丸</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>https://kurokawamaru.net/</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>（五目） ※平潟湾の釣り船。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I116" s="3" t="inlineStr">
+        <is>
+          <t>午前+午後通し 3,500円 ※一律・エサ/コマセ/氷付（公式プラン記載）</t>
+        </is>
+      </c>
+      <c r="J116" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>横須賀市</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>長井新宿</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>辰丸</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>https://tatsumaru-nagai.com/</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>スルメイカ ※1963年創業のイカ専門（スルメ・ヤリ・アカ・マルイカ五目）。女性・中学生以下割引。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I117" s="3" t="inlineStr"/>
+      <c r="J117" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>横須賀市</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>長井新宿</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>栃木丸</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>https://tochigimaru.jp/</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>ヤリイカ ※40年超の歴史・3代目。周年ヤリ・スルメ狙い（剣崎沖・城ヶ島沖）。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I118" s="3" t="inlineStr"/>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>三浦市</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>三崎</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>佐円丸</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>https://saenmaru.jp/</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>ヤリイカ ※イカ各種＋キンメ・アコウダイ・ワラサ・オニカサゴ・カワハギ等。釣り物別料金・家族/カップル割あり。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I119" s="3" t="inlineStr"/>
+      <c r="J119" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>三浦市</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>間口</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>千良丸</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chiyoshimaru.com/</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>（五目） ※間口漁港の釣り船。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I120" s="3" t="inlineStr"/>
+      <c r="J120" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>三浦市</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>間口</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>育丸</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ikumaru190.com/</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>仕立中心</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>（業態メモ） ※仕立専門・3隻体制（現役漁師の船長、最新ソナー搭載）。日次乗合釣果は非公開</t>
+        </is>
+      </c>
+      <c r="I121" s="3" t="inlineStr"/>
+      <c r="J121" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>三浦市</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>間口</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>丸又丸</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marumatamaru.net/</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>オニカサゴ ※14m・4.9t・定員13名・ソナー装備。直近実績はオニカサゴ。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I122" s="3" t="inlineStr"/>
+      <c r="J122" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>釣割</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>三浦市</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>間口</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>鈴茂丸</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>https://suzushigemaru.com/</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>仕立中心</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>（業態メモ） ※間口港のフルサービス仕立船。数値釣果は非公開</t>
+        </is>
+      </c>
+      <c r="I123" s="3" t="inlineStr"/>
+      <c r="J123" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>真鶴町</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>真鶴</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>八十吉丸</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>http://yasokitimaru.main.jp/</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>乗合</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>（五目） ※真鶴港の釣船。予約24時間受付・ライフジャケット無料貸出。数値釣果は未取得</t>
+        </is>
+      </c>
+      <c r="I124" s="3" t="inlineStr"/>
+      <c r="J124" s="5" t="inlineStr">
+        <is>
+          <t>一部</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>公式サイト</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="n">
         <v>0</v>
       </c>
     </row>
